--- a/artfynd/S 3363-2025 artfynd.xlsx
+++ b/artfynd/S 3363-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY158"/>
+  <dimension ref="A1:AZ158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132839452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129870022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129811441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129811485</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129811505</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129812794</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129815700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129816268</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820034</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820166</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822007</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822043</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2417,6 +2497,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822115</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2524,6 +2609,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825358</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,6 +2721,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825433</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2738,6 +2833,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129826375</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2845,6 +2945,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828650</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2952,6 +3057,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828801</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3059,6 +3169,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3166,6 +3281,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828949</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3273,6 +3393,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828988</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3380,6 +3505,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129829081</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3487,6 +3617,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129829098</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3594,6 +3729,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129829116</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3701,6 +3841,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129829402</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3808,6 +3953,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869380</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3915,6 +4065,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869314</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4022,6 +4177,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869861</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4129,6 +4289,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869712</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4236,6 +4401,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869924</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4343,6 +4513,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129870039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4450,6 +4625,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129870025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4557,6 +4737,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129870831</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4669,6 +4854,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871153</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4776,6 +4966,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871239</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4883,6 +5078,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871250</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4990,6 +5190,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871264</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5097,6 +5302,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871295</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5204,6 +5414,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871319</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5311,6 +5526,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871331</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5418,6 +5638,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871362</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5525,6 +5750,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871457</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5632,6 +5862,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871469</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5739,6 +5974,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871522</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5846,6 +6086,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871529</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5953,6 +6198,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871533</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6060,6 +6310,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871561</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6167,6 +6422,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871591</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6274,6 +6534,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871756</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6381,6 +6646,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880256</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6488,6 +6758,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880319</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6595,6 +6870,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880422</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6702,6 +6982,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880438</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6809,6 +7094,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880593</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6916,6 +7206,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880771</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7028,6 +7323,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881700</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7135,6 +7435,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881723</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7247,6 +7552,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881833</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7354,6 +7664,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881892</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7466,6 +7781,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881943</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7578,6 +7898,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129882383</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7685,6 +8010,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129882657</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7792,6 +8122,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884258</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7899,6 +8234,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884271</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8006,6 +8346,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884286</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8118,6 +8463,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129885741</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8225,6 +8575,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129886537</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8332,6 +8687,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129887462</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8439,6 +8799,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129887591</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8546,6 +8911,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129888086</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8658,6 +9028,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129889660</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8770,6 +9145,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129889738</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8877,6 +9257,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129890213</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8984,6 +9369,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129890431</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9091,6 +9481,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180800</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9198,6 +9593,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180807</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9310,6 +9710,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180902</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9422,6 +9827,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181090</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9529,6 +9939,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181142</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9641,6 +10056,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181224</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9748,6 +10168,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181366</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9855,6 +10280,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181984</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9962,6 +10392,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130182426</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10069,6 +10504,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130182816</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10176,6 +10616,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130183682</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10283,6 +10728,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184203</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10390,6 +10840,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130185383</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10497,6 +10952,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130186243</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10604,6 +11064,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187336</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10711,6 +11176,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130189460</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10818,6 +11288,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191033</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10925,6 +11400,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191890</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11032,6 +11512,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192984</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11139,6 +11624,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193066</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11246,6 +11736,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193185</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11353,6 +11848,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193825</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11460,6 +11960,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130194038</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11567,6 +12072,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130194071</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11679,6 +12189,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130195073</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11786,6 +12301,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130196270</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11893,6 +12413,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130196675</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11994,6 +12519,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958131</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12095,6 +12625,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967232</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12192,6 +12727,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959581</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12289,6 +12829,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966395</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12396,6 +12941,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129816004</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12503,6 +13053,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129826366</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12610,6 +13165,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130186199</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12717,6 +13277,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187277</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12824,6 +13389,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191865</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12931,6 +13501,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130196268</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13043,6 +13618,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129812625</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13155,6 +13735,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129815480</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13267,6 +13852,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820161</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13379,6 +13969,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871883</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13491,6 +14086,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129878240</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13603,6 +14203,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880255</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13715,6 +14320,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880884</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13827,6 +14437,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881718</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13939,6 +14554,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884227</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14056,6 +14676,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130183670</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14168,6 +14793,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130189420</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14280,6 +14910,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129826346</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14392,6 +15027,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869703</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14499,6 +15139,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129869928</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14616,6 +15261,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871309</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14728,6 +15378,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871451</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14845,6 +15500,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129871618</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14960,6 +15620,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129872338</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15072,6 +15737,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129890901</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15184,6 +15854,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181365</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15296,6 +15971,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181459</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15408,6 +16088,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181983</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15525,6 +16210,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130182063</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15645,6 +16335,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130182811</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15762,6 +16457,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130183546</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15879,6 +16579,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184259</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15991,6 +16696,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191008</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16103,6 +16813,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130196359</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16215,6 +16930,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130196609</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16324,6 +17044,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129836641</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16440,6 +17165,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129819365</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16547,6 +17277,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129814978</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16659,6 +17394,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129815577</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16771,6 +17511,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820163</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16883,6 +17628,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822046</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16995,6 +17745,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825510</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17107,6 +17862,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129879101</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17219,6 +17979,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880264</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17331,6 +18096,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884204</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17438,6 +18208,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129888863</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17545,6 +18320,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192979</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17646,6 +18426,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965976</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17747,8 +18532,172 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3363-2025 artfynd.xlsx
+++ b/artfynd/S 3363-2025 artfynd.xlsx
@@ -12424,7 +12424,7 @@
         <v>134958131</v>
       </c>
       <c r="B106" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>134967232</v>
       </c>
       <c r="B107" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>134959581</v>
       </c>
       <c r="B108" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>134966395</v>
       </c>
       <c r="B109" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>134965976</v>
       </c>
       <c r="B157" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>134967863</v>
       </c>
       <c r="B158" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
